--- a/output/ap_payment_opening_db/未匹配清单_应付期初_20260619.xlsx
+++ b/output/ap_payment_opening_db/未匹配清单_应付期初_20260619.xlsx
@@ -10,6 +10,7 @@
     <sheet name="必输字段未达100%" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="缺失_收款方编码" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="缺失_费用项目编码" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="银行账号_校验异常" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,10 +461,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>5191</v>
+        <v>5192</v>
       </c>
       <c r="D2" t="n">
-        <v>5191</v>
+        <v>5192</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -479,13 +480,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4969</v>
+        <v>4970</v>
       </c>
       <c r="C3" t="n">
         <v>222</v>
       </c>
       <c r="D3" t="n">
-        <v>5191</v>
+        <v>5192</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -501,13 +502,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5081</v>
+        <v>5082</v>
       </c>
       <c r="C4" t="n">
         <v>110</v>
       </c>
       <c r="D4" t="n">
-        <v>5191</v>
+        <v>5192</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3523,4 +3524,2331 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>来源单据编号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>收款方编码</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>源银行账号</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>输出银行账号</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Hand默认银行账号</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Hand可用银行账号数</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>F1-A2-2026-011-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-6288</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>121910114610502</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-013-0005</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-6929</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3922427174</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>31050181410000003097</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31050181410000003097</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-027-0143</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0016</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>68623700001481</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-027-0141</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-027-0140</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-027-0139</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-027-0138</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F1-A1-2025-019-0212</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-EQP-0001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-311-0001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TAL-0015</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>149-100360-56-00010</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-027-0149</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TAL-0194</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>62891000303938</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F1-A1-2025-019-0213</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-EQP-0001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F1-A1-2025-019-0214</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-EQP-0001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F1-A1-2025-019-0215</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-EQP-0001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-287-0009</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-TAL-0044</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>101-927477-6</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-312-0011</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TAL-0194</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>62891000303938</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-287-0002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TAL-0194</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>62891000303938</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-312-0022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TAL-0194</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>62891000303938</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>F1-A3-2026-001-0006</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-4289</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>551548616311</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-304-0005</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-TPS-0476</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SE4350000000051503016188</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>121952073910001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>121952073910001</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>F1-Y2-2026-009-0001</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-OPS-0182</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7062049264</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>000251087530</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>000251087530</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-196-0080</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V-I-OS-SP-TAL-0138</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7501087097</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-314-0004</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-027-0192</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-TAL-0425</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3915485803</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-314-0017</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>F1-A4-2026-007-0021</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>V-C-CN-AD-TRA-0014</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>50100861357858</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>122905939910108</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>122905939910108</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F1-A4-2026-007-0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>V-C-CN-AD-TRA-0014</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>647-0056467</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>122905939910108</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>122905939910108</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>F1-A3-2026-001-0031</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-4289</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>551548616311</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-312-0034</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-TAL-0425</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3915485803</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>F1-A4-2026-007-0042</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>V-C-CN-AD-TRA-0003</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1492504412</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>606740096</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>606740096</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-004-0041</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-6262</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>62891000303938</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>405280667800</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>405280667800</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-037-0001</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-037-0002</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-037-0003</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>V-I-OS-SP-TPS-0006</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1005-204-066415</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-082-0003</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-081-0005</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V-I-OS-SP-TPS-0235</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>29291024936007</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-082-0009</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>F1-A3-2026-001-0077</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-4289</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>551548616311</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-047-0011</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-EQP-0001</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>F1-B2-2025-301-0015</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-TPS-0615</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>310069202015004032490</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>＇310069202015004032490</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>＇310069202015004032490</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-115-0001</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>F1-A3-2026-004-0002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>017000</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8901309192</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>98400078801800002379</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>98400078801800002379</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-081-0006</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>V-I-OS-SP-TPS-0233</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>38791028729107</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>F1-A2-2026-024-0021</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-4289</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>551548616311</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-081-0007</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-081-0008</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-081-0009</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-081-0017</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>V-I-OS-SP-TPS-0004</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1002-133-242503</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-088-0002</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-088-0001</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-023-0010</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>F1-A1-2025-028-0006</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>V-C-CN-IT-CLO-0001</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1109073168100090004938022</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>17</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>F1-A3-2026-001-0105</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-4289</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>551548616311</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>F1-Y2-2026-003-0061</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-OPS-0092</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7321052657</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>229931512419</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>229931512419</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>F1-Y2-2026-003-0062</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-OPS-0092</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>15301600468591</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>229931512419</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>229931512419</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-009-0017</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>F1-A1-2026-022-0008</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-EQP-0001</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>F1-A1-2025-028-0008</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>V-C-CN-IT-CLO-0001</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1109073168100090004938022</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>17</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-145-0003</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>F1-B7-2026-003-0016</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>V-C-CN-MC-ADV-0095</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>JO84IIBA1360000001360000552500</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>729800002036</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>729800002036</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-097-0010</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>F1-A3-2026-001-0145</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>V-C-CN-OT-OTH-4289</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>551548616311</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0110363044</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-177-0003</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-017-0020</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-EXP-0009</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>310069202015004032490</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3602085609100124226</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3602085609100124226</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-164-0003</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>F1-B5-2025-001-0038</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>V-C-CN-IT-CLO-0001</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1109073168100090004936658</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>17</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-178-0010</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>V-I-OS-SP-TPS-0247</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>143-248310-5</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0261592037</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0261592037</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>F1-B5-2025-001-0042</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>V-C-CN-IT-CLO-0001</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1109073168100090004668471</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>17</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-145-0019</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>V-C-CN-AD-TRA-0142</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>97150154740000448</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>9715015470000448</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>9715015470000448</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>F1-A1-2025-028-0011</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>V-C-CN-IT-CLO-0001</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1109073168100090004938022</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1109073168106010003246210</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>17</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-195-0002</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-145-0031</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SMC-0052</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>31598503000259801</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>31001648001059730096</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>31001648001059730096</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-131-0035</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>V-C-CN-SP-SCM-0010</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>09411601040045831</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-190-0005</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>V-C-OS-SP-TPS-0011</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>298-910037-375204</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>F1-B2-2026-190-0006</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>V-I-OS-SP-TPS-0004</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1002-133-242503</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>F1-A2-2026-044-0004</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>V-C-CN-PS-PRS-0021</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>000111333</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>000111351</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>000111351</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>源银行账号未在该收款方Hand供应商银行卡中找到,已使用默认银行账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>F1-A1-2025-020-0090</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>V-I-CN-SP-EQP-0001</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>收款方在Hand供应商银行卡中未找到可用银行账号</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>